--- a/resources/HEARTH_Script_Breakdown_Sheet.xlsx
+++ b/resources/HEARTH_Script_Breakdown_Sheet.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="101">
   <si>
     <t xml:space="preserve">HEARTH  ·  Script Breakdown Sheet</t>
   </si>
@@ -207,6 +207,9 @@
   </si>
   <si>
     <t xml:space="preserve">TOTALS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEARTH  ·  Production Resource Library  ·  buildyourhearth.studio</t>
   </si>
   <si>
     <t xml:space="preserve">HEARTH  ·  Element Breakdown by Category</t>
@@ -331,7 +334,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -396,6 +399,14 @@
     <font>
       <sz val="10"/>
       <color rgb="FF0D1B2E"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="8"/>
+      <color rgb="FF888898"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -579,11 +590,15 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -648,7 +663,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -656,19 +671,23 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -676,23 +695,23 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="14" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="14" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="15" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="15" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -722,7 +741,7 @@
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFCDC8BE"/>
-      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF888898"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF7A4A0A"/>
       <rgbColor rgb="FFF5F0E8"/>
@@ -948,706 +967,723 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:L45"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="9" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="9" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="3"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="2" t="s">
+      <c r="C4" s="4"/>
+      <c r="D4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="2" t="s">
+      <c r="E4" s="4"/>
+      <c r="F4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="2" t="s">
+      <c r="G4" s="4"/>
+      <c r="H4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="2" t="s">
+      <c r="I4" s="4"/>
+      <c r="J4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="3"/>
+      <c r="K4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="L6" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="I8" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7" t="s">
+      <c r="K8" s="8"/>
+      <c r="L8" s="8" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="I9" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="J9" s="9" t="s">
+      <c r="J9" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="K9" s="9" t="s">
+      <c r="K9" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="L9" s="9" t="s">
+      <c r="L9" s="10" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="H10" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="J10" s="11" t="s">
+      <c r="J10" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11" t="s">
+      <c r="K10" s="12"/>
+      <c r="L10" s="12" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="G11" s="13" t="s">
+      <c r="G11" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="H11" s="13" t="s">
+      <c r="H11" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13" t="s">
+      <c r="I11" s="14"/>
+      <c r="J11" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="K11" s="13" t="s">
+      <c r="K11" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="L11" s="13" t="s">
+      <c r="L11" s="14" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="I12" s="7" t="s">
+      <c r="I12" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="J12" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7" t="s">
+      <c r="K12" s="8"/>
+      <c r="L12" s="8" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
     </row>
     <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
     </row>
     <row r="16" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="17"/>
     </row>
     <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="17"/>
     </row>
     <row r="18" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="17"/>
     </row>
     <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="17"/>
     </row>
     <row r="20" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="16"/>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="17"/>
     </row>
     <row r="21" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="17"/>
     </row>
     <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="16"/>
-      <c r="J22" s="16"/>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="17"/>
     </row>
     <row r="23" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
     </row>
     <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="17"/>
     </row>
     <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="17"/>
     </row>
     <row r="26" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="16"/>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="17"/>
     </row>
     <row r="27" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16"/>
-      <c r="J27" s="16"/>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="17"/>
     </row>
     <row r="28" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="16"/>
-      <c r="J28" s="16"/>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
     </row>
     <row r="29" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="16"/>
-      <c r="I29" s="16"/>
-      <c r="J29" s="16"/>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17"/>
     </row>
     <row r="30" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="16"/>
-      <c r="I30" s="16"/>
-      <c r="J30" s="16"/>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="17"/>
+      <c r="J30" s="17"/>
+      <c r="K30" s="17"/>
+      <c r="L30" s="17"/>
     </row>
     <row r="31" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="15"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
+      <c r="B31" s="16"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="17"/>
+      <c r="L31" s="17"/>
     </row>
     <row r="32" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="15"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16"/>
-      <c r="I32" s="16"/>
-      <c r="J32" s="16"/>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="17"/>
+      <c r="K32" s="17"/>
+      <c r="L32" s="17"/>
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="15"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="16"/>
-      <c r="H33" s="16"/>
-      <c r="I33" s="16"/>
-      <c r="J33" s="16"/>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17"/>
+      <c r="J33" s="17"/>
+      <c r="K33" s="17"/>
+      <c r="L33" s="17"/>
     </row>
     <row r="34" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="15"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
-      <c r="I34" s="16"/>
-      <c r="J34" s="16"/>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="17"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="17"/>
+      <c r="L34" s="17"/>
     </row>
     <row r="35" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="15"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="16"/>
-      <c r="H35" s="16"/>
-      <c r="I35" s="16"/>
-      <c r="J35" s="16"/>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="17"/>
+      <c r="I35" s="17"/>
+      <c r="J35" s="17"/>
+      <c r="K35" s="17"/>
+      <c r="L35" s="17"/>
     </row>
     <row r="36" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="15"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="16"/>
-      <c r="H36" s="16"/>
-      <c r="I36" s="16"/>
-      <c r="J36" s="16"/>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
+      <c r="B36" s="16"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="17"/>
+      <c r="J36" s="17"/>
+      <c r="K36" s="17"/>
+      <c r="L36" s="17"/>
     </row>
     <row r="37" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="15"/>
-      <c r="C37" s="15"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="16"/>
-      <c r="H37" s="16"/>
-      <c r="I37" s="16"/>
-      <c r="J37" s="16"/>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
+      <c r="B37" s="16"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="17"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="17"/>
+      <c r="L37" s="17"/>
     </row>
     <row r="38" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="16"/>
-      <c r="I38" s="16"/>
-      <c r="J38" s="16"/>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
+      <c r="B38" s="16"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="17"/>
+      <c r="K38" s="17"/>
+      <c r="L38" s="17"/>
     </row>
     <row r="39" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="15"/>
-      <c r="C39" s="15"/>
-      <c r="D39" s="15"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="15"/>
-      <c r="G39" s="16"/>
-      <c r="H39" s="16"/>
-      <c r="I39" s="16"/>
-      <c r="J39" s="16"/>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
+      <c r="B39" s="16"/>
+      <c r="C39" s="16"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="17"/>
+      <c r="J39" s="17"/>
+      <c r="K39" s="17"/>
+      <c r="L39" s="17"/>
     </row>
     <row r="40" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="15"/>
-      <c r="C40" s="15"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="15"/>
-      <c r="G40" s="16"/>
-      <c r="H40" s="16"/>
-      <c r="I40" s="16"/>
-      <c r="J40" s="16"/>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
+      <c r="B40" s="16"/>
+      <c r="C40" s="16"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="16"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="17"/>
+      <c r="K40" s="17"/>
+      <c r="L40" s="17"/>
     </row>
     <row r="41" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="15"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="15"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="15"/>
-      <c r="G41" s="16"/>
-      <c r="H41" s="16"/>
-      <c r="I41" s="16"/>
-      <c r="J41" s="16"/>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
+      <c r="B41" s="16"/>
+      <c r="C41" s="16"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="16"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="17"/>
+      <c r="I41" s="17"/>
+      <c r="J41" s="17"/>
+      <c r="K41" s="17"/>
+      <c r="L41" s="17"/>
     </row>
     <row r="42" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="15"/>
-      <c r="C42" s="15"/>
-      <c r="D42" s="15"/>
-      <c r="E42" s="15"/>
-      <c r="F42" s="15"/>
-      <c r="G42" s="16"/>
-      <c r="H42" s="16"/>
-      <c r="I42" s="16"/>
-      <c r="J42" s="16"/>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
+      <c r="B42" s="16"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="17"/>
+      <c r="I42" s="17"/>
+      <c r="J42" s="17"/>
+      <c r="K42" s="17"/>
+      <c r="L42" s="17"/>
     </row>
     <row r="43" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="15"/>
-      <c r="C43" s="15"/>
-      <c r="D43" s="15"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="15"/>
-      <c r="G43" s="16"/>
-      <c r="H43" s="16"/>
-      <c r="I43" s="16"/>
-      <c r="J43" s="16"/>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
+      <c r="B43" s="16"/>
+      <c r="C43" s="16"/>
+      <c r="D43" s="16"/>
+      <c r="E43" s="16"/>
+      <c r="F43" s="16"/>
+      <c r="G43" s="17"/>
+      <c r="H43" s="17"/>
+      <c r="I43" s="17"/>
+      <c r="J43" s="17"/>
+      <c r="K43" s="17"/>
+      <c r="L43" s="17"/>
     </row>
     <row r="44" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="15"/>
-      <c r="C44" s="15"/>
-      <c r="D44" s="15"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="15"/>
-      <c r="G44" s="16"/>
-      <c r="H44" s="16"/>
-      <c r="I44" s="16"/>
-      <c r="J44" s="16"/>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
+      <c r="B44" s="16"/>
+      <c r="C44" s="16"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="17"/>
+      <c r="I44" s="17"/>
+      <c r="J44" s="17"/>
+      <c r="K44" s="17"/>
+      <c r="L44" s="17"/>
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="17" t="s">
+      <c r="B45" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="C45" s="18" t="n">
+      <c r="C45" s="19" t="n">
         <f aca="false">SUM(C8:C44)</f>
         <v>0</v>
       </c>
-      <c r="D45" s="19"/>
-      <c r="E45" s="19"/>
-      <c r="F45" s="19"/>
-      <c r="G45" s="19"/>
-      <c r="H45" s="19"/>
-      <c r="I45" s="19"/>
-      <c r="J45" s="19"/>
-      <c r="K45" s="19"/>
-      <c r="L45" s="19"/>
+      <c r="D45" s="20"/>
+      <c r="E45" s="20"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="20"/>
+      <c r="H45" s="20"/>
+      <c r="I45" s="20"/>
+      <c r="J45" s="20"/>
+      <c r="K45" s="20"/>
+      <c r="L45" s="20"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="B47" s="21"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="21"/>
+      <c r="E47" s="21"/>
+      <c r="F47" s="21"/>
+      <c r="G47" s="21"/>
+      <c r="H47" s="21"/>
+      <c r="I47" s="21"/>
+      <c r="J47" s="21"/>
+      <c r="K47" s="21"/>
+      <c r="L47" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="B2:L2"/>
     <mergeCell ref="B7:L7"/>
     <mergeCell ref="B14:L14"/>
+    <mergeCell ref="A47:L47"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1667,397 +1703,397 @@
   <dimension ref="B1:D62"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="3"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="B2" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
     </row>
     <row r="3" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
+      <c r="B4" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="22" t="s">
+      <c r="B5" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="C5" s="24" t="s">
         <v>66</v>
       </c>
+      <c r="D5" s="24" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="16"/>
+      <c r="B6" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17"/>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="23" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" s="15"/>
-      <c r="D7" s="16"/>
+      <c r="B7" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="17"/>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="15"/>
-      <c r="D8" s="16"/>
+      <c r="B8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17"/>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="15"/>
-      <c r="D9" s="16"/>
+      <c r="B9" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="16"/>
+      <c r="D9" s="17"/>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" s="15"/>
-      <c r="D10" s="16"/>
+      <c r="B10" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="23" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" s="15"/>
-      <c r="D11" s="16"/>
+      <c r="B11" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="16"/>
+      <c r="D11" s="17"/>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="15"/>
-      <c r="D12" s="16"/>
+      <c r="B12" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" s="16"/>
+      <c r="D12" s="17"/>
     </row>
     <row r="13" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
+      <c r="B14" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="C15" s="22" t="s">
+      <c r="B15" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="C15" s="24" t="s">
         <v>66</v>
       </c>
+      <c r="D15" s="24" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="16"/>
+      <c r="B16" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="16"/>
+      <c r="D16" s="17"/>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" s="15"/>
-      <c r="D17" s="16"/>
+      <c r="B17" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" s="16"/>
+      <c r="D17" s="17"/>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18" s="15"/>
-      <c r="D18" s="16"/>
+      <c r="B18" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="16"/>
+      <c r="B19" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" s="16"/>
+      <c r="D19" s="17"/>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C20" s="15"/>
-      <c r="D20" s="16"/>
+      <c r="B20" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="16"/>
+      <c r="D20" s="17"/>
     </row>
     <row r="21" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
+      <c r="B22" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22" s="27"/>
+      <c r="D22" s="27"/>
     </row>
     <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="C23" s="22" t="s">
+      <c r="B23" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="D23" s="22" t="s">
+      <c r="C23" s="24" t="s">
         <v>66</v>
       </c>
+      <c r="D23" s="24" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="16"/>
+      <c r="B24" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24" s="16"/>
+      <c r="D24" s="17"/>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="23"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="16"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="17"/>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="2"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="16"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="23"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="16"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="17"/>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="2"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="16"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="17"/>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="23"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="16"/>
+      <c r="B29" s="25"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="17"/>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="2"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="16"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="23"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="16"/>
+      <c r="B31" s="25"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="17"/>
     </row>
     <row r="32" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="C33" s="26"/>
-      <c r="D33" s="26"/>
+      <c r="B33" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
     </row>
     <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="C34" s="22" t="s">
+      <c r="B34" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="D34" s="22" t="s">
+      <c r="C34" s="24" t="s">
         <v>66</v>
       </c>
+      <c r="D34" s="24" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="C35" s="15"/>
-      <c r="D35" s="16"/>
+      <c r="B35" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="C35" s="16"/>
+      <c r="D35" s="17"/>
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C36" s="15"/>
-      <c r="D36" s="16"/>
+      <c r="B36" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C36" s="16"/>
+      <c r="D36" s="17"/>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="C37" s="15"/>
-      <c r="D37" s="16"/>
+      <c r="B37" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37" s="16"/>
+      <c r="D37" s="17"/>
     </row>
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C38" s="15"/>
-      <c r="D38" s="16"/>
+      <c r="B38" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C38" s="16"/>
+      <c r="D38" s="17"/>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="23"/>
-      <c r="C39" s="15"/>
-      <c r="D39" s="16"/>
+      <c r="B39" s="25"/>
+      <c r="C39" s="16"/>
+      <c r="D39" s="17"/>
     </row>
     <row r="40" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="27" t="s">
-        <v>87</v>
-      </c>
-      <c r="C41" s="27"/>
-      <c r="D41" s="27"/>
+      <c r="B41" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="C41" s="29"/>
+      <c r="D41" s="29"/>
     </row>
     <row r="42" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="C42" s="22" t="s">
+      <c r="B42" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="D42" s="22" t="s">
+      <c r="C42" s="24" t="s">
         <v>66</v>
       </c>
+      <c r="D42" s="24" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="C43" s="15"/>
-      <c r="D43" s="16"/>
+      <c r="B43" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="C43" s="16"/>
+      <c r="D43" s="17"/>
     </row>
     <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C44" s="15"/>
-      <c r="D44" s="16"/>
+      <c r="B44" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C44" s="16"/>
+      <c r="D44" s="17"/>
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="C45" s="15"/>
-      <c r="D45" s="16"/>
+      <c r="B45" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="C45" s="16"/>
+      <c r="D45" s="17"/>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C46" s="15"/>
-      <c r="D46" s="16"/>
+      <c r="B46" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C46" s="16"/>
+      <c r="D46" s="17"/>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="C47" s="15"/>
-      <c r="D47" s="16"/>
+      <c r="B47" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C47" s="16"/>
+      <c r="D47" s="17"/>
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="2"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="16"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="16"/>
+      <c r="D48" s="17"/>
     </row>
     <row r="49" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="C50" s="28"/>
-      <c r="D50" s="28"/>
+      <c r="B50" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="C50" s="30"/>
+      <c r="D50" s="30"/>
     </row>
     <row r="51" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B51" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="C51" s="22" t="s">
+      <c r="B51" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="D51" s="22" t="s">
+      <c r="C51" s="24" t="s">
         <v>66</v>
       </c>
+      <c r="D51" s="24" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C52" s="15"/>
-      <c r="D52" s="16"/>
+      <c r="B52" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C52" s="16"/>
+      <c r="D52" s="17"/>
     </row>
     <row r="53" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="C53" s="15"/>
-      <c r="D53" s="16"/>
+      <c r="B53" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="C53" s="16"/>
+      <c r="D53" s="17"/>
     </row>
     <row r="54" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B54" s="2"/>
-      <c r="C54" s="15"/>
-      <c r="D54" s="16"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="17"/>
     </row>
     <row r="55" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B56" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="C56" s="28"/>
-      <c r="D56" s="28"/>
+      <c r="B56" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="C56" s="30"/>
+      <c r="D56" s="30"/>
     </row>
     <row r="57" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B57" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="C57" s="22" t="s">
+      <c r="B57" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="D57" s="22" t="s">
+      <c r="C57" s="24" t="s">
         <v>66</v>
       </c>
+      <c r="D57" s="24" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B58" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C58" s="15"/>
-      <c r="D58" s="16"/>
+      <c r="B58" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C58" s="16"/>
+      <c r="D58" s="17"/>
     </row>
     <row r="59" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B59" s="23" t="s">
-        <v>98</v>
-      </c>
-      <c r="C59" s="15"/>
-      <c r="D59" s="16"/>
+      <c r="B59" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="C59" s="16"/>
+      <c r="D59" s="17"/>
     </row>
     <row r="60" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B60" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C60" s="15"/>
-      <c r="D60" s="16"/>
+      <c r="B60" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C60" s="16"/>
+      <c r="D60" s="17"/>
     </row>
     <row r="61" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B61" s="23"/>
-      <c r="C61" s="15"/>
-      <c r="D61" s="16"/>
+      <c r="B61" s="25"/>
+      <c r="C61" s="16"/>
+      <c r="D61" s="17"/>
     </row>
     <row r="62" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>

--- a/resources/HEARTH_Script_Breakdown_Sheet.xlsx
+++ b/resources/HEARTH_Script_Breakdown_Sheet.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="100">
   <si>
     <t xml:space="preserve">HEARTH  ·  Script Breakdown Sheet</t>
   </si>
@@ -207,9 +207,6 @@
   </si>
   <si>
     <t xml:space="preserve">TOTALS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HEARTH  ·  Production Resource Library  ·  buildyourhearth.studio</t>
   </si>
   <si>
     <t xml:space="preserve">HEARTH  ·  Element Breakdown by Category</t>
@@ -334,7 +331,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -399,14 +396,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FF0D1B2E"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="8"/>
-      <color rgb="FF888898"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -590,15 +579,11 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="29">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -663,7 +648,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -671,23 +656,19 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -695,23 +676,23 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="14" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="14" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="15" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="15" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -741,7 +722,7 @@
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFCDC8BE"/>
-      <rgbColor rgb="FF888898"/>
+      <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF7A4A0A"/>
       <rgbColor rgb="FFF5F0E8"/>
@@ -967,723 +948,706 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L47"/>
+  <dimension ref="B1:L45"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="9" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="9" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="3"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="3" t="s">
+      <c r="C4" s="3"/>
+      <c r="D4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="3" t="s">
+      <c r="E4" s="3"/>
+      <c r="F4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="3" t="s">
+      <c r="G4" s="3"/>
+      <c r="H4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="3" t="s">
+      <c r="I4" s="3"/>
+      <c r="J4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="4"/>
+      <c r="K4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="K6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="L6" s="5" t="s">
+      <c r="L6" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="J8" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8" t="s">
+      <c r="K8" s="7"/>
+      <c r="L8" s="7" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="I9" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="J9" s="10" t="s">
+      <c r="J9" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="K9" s="10" t="s">
+      <c r="K9" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="L9" s="10" t="s">
+      <c r="L9" s="9" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="H10" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="I10" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="J10" s="12" t="s">
+      <c r="J10" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12" t="s">
+      <c r="K10" s="11"/>
+      <c r="L10" s="11" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G11" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="H11" s="14" t="s">
+      <c r="H11" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14" t="s">
+      <c r="I11" s="13"/>
+      <c r="J11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="K11" s="14" t="s">
+      <c r="K11" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="L11" s="14" t="s">
+      <c r="L11" s="13" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="H12" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="J12" s="8" t="s">
+      <c r="J12" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8" t="s">
+      <c r="K12" s="7"/>
+      <c r="L12" s="7" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="14"/>
     </row>
     <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
     </row>
     <row r="16" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="17"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
     </row>
     <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="17"/>
-      <c r="L17" s="17"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
     </row>
     <row r="18" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="17"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
     </row>
     <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="17"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="16"/>
+      <c r="L19" s="16"/>
     </row>
     <row r="20" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="17"/>
-      <c r="L20" s="17"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="16"/>
+      <c r="K20" s="16"/>
+      <c r="L20" s="16"/>
     </row>
     <row r="21" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
-      <c r="L21" s="17"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="16"/>
+      <c r="K21" s="16"/>
+      <c r="L21" s="16"/>
     </row>
     <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="17"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="16"/>
+      <c r="J22" s="16"/>
+      <c r="K22" s="16"/>
+      <c r="L22" s="16"/>
     </row>
     <row r="23" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="17"/>
-      <c r="L23" s="17"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="16"/>
+      <c r="K23" s="16"/>
+      <c r="L23" s="16"/>
     </row>
     <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
-      <c r="L24" s="17"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="16"/>
+      <c r="K24" s="16"/>
+      <c r="L24" s="16"/>
     </row>
     <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
-      <c r="L25" s="17"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="16"/>
+      <c r="K25" s="16"/>
+      <c r="L25" s="16"/>
     </row>
     <row r="26" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="17"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="16"/>
+      <c r="J26" s="16"/>
+      <c r="K26" s="16"/>
+      <c r="L26" s="16"/>
     </row>
     <row r="27" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="17"/>
-      <c r="L27" s="17"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="16"/>
+      <c r="I27" s="16"/>
+      <c r="J27" s="16"/>
+      <c r="K27" s="16"/>
+      <c r="L27" s="16"/>
     </row>
     <row r="28" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="17"/>
-      <c r="L28" s="17"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="16"/>
+      <c r="J28" s="16"/>
+      <c r="K28" s="16"/>
+      <c r="L28" s="16"/>
     </row>
     <row r="29" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="16"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="17"/>
-      <c r="I29" s="17"/>
-      <c r="J29" s="17"/>
-      <c r="K29" s="17"/>
-      <c r="L29" s="17"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="16"/>
+      <c r="I29" s="16"/>
+      <c r="J29" s="16"/>
+      <c r="K29" s="16"/>
+      <c r="L29" s="16"/>
     </row>
     <row r="30" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="16"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="17"/>
-      <c r="J30" s="17"/>
-      <c r="K30" s="17"/>
-      <c r="L30" s="17"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="16"/>
+      <c r="I30" s="16"/>
+      <c r="J30" s="16"/>
+      <c r="K30" s="16"/>
+      <c r="L30" s="16"/>
     </row>
     <row r="31" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="16"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
-      <c r="J31" s="17"/>
-      <c r="K31" s="17"/>
-      <c r="L31" s="17"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="16"/>
+      <c r="H31" s="16"/>
+      <c r="I31" s="16"/>
+      <c r="J31" s="16"/>
+      <c r="K31" s="16"/>
+      <c r="L31" s="16"/>
     </row>
     <row r="32" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="16"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="17"/>
-      <c r="I32" s="17"/>
-      <c r="J32" s="17"/>
-      <c r="K32" s="17"/>
-      <c r="L32" s="17"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="16"/>
+      <c r="I32" s="16"/>
+      <c r="J32" s="16"/>
+      <c r="K32" s="16"/>
+      <c r="L32" s="16"/>
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="16"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="17"/>
-      <c r="I33" s="17"/>
-      <c r="J33" s="17"/>
-      <c r="K33" s="17"/>
-      <c r="L33" s="17"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="16"/>
+      <c r="I33" s="16"/>
+      <c r="J33" s="16"/>
+      <c r="K33" s="16"/>
+      <c r="L33" s="16"/>
     </row>
     <row r="34" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="16"/>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="17"/>
-      <c r="I34" s="17"/>
-      <c r="J34" s="17"/>
-      <c r="K34" s="17"/>
-      <c r="L34" s="17"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="16"/>
+      <c r="I34" s="16"/>
+      <c r="J34" s="16"/>
+      <c r="K34" s="16"/>
+      <c r="L34" s="16"/>
     </row>
     <row r="35" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="16"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="17"/>
-      <c r="H35" s="17"/>
-      <c r="I35" s="17"/>
-      <c r="J35" s="17"/>
-      <c r="K35" s="17"/>
-      <c r="L35" s="17"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="16"/>
+      <c r="I35" s="16"/>
+      <c r="J35" s="16"/>
+      <c r="K35" s="16"/>
+      <c r="L35" s="16"/>
     </row>
     <row r="36" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="16"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="17"/>
-      <c r="H36" s="17"/>
-      <c r="I36" s="17"/>
-      <c r="J36" s="17"/>
-      <c r="K36" s="17"/>
-      <c r="L36" s="17"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="16"/>
+      <c r="H36" s="16"/>
+      <c r="I36" s="16"/>
+      <c r="J36" s="16"/>
+      <c r="K36" s="16"/>
+      <c r="L36" s="16"/>
     </row>
     <row r="37" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="16"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16"/>
-      <c r="G37" s="17"/>
-      <c r="H37" s="17"/>
-      <c r="I37" s="17"/>
-      <c r="J37" s="17"/>
-      <c r="K37" s="17"/>
-      <c r="L37" s="17"/>
+      <c r="B37" s="15"/>
+      <c r="C37" s="15"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="15"/>
+      <c r="G37" s="16"/>
+      <c r="H37" s="16"/>
+      <c r="I37" s="16"/>
+      <c r="J37" s="16"/>
+      <c r="K37" s="16"/>
+      <c r="L37" s="16"/>
     </row>
     <row r="38" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="16"/>
-      <c r="C38" s="16"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="17"/>
-      <c r="H38" s="17"/>
-      <c r="I38" s="17"/>
-      <c r="J38" s="17"/>
-      <c r="K38" s="17"/>
-      <c r="L38" s="17"/>
+      <c r="B38" s="15"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="16"/>
+      <c r="H38" s="16"/>
+      <c r="I38" s="16"/>
+      <c r="J38" s="16"/>
+      <c r="K38" s="16"/>
+      <c r="L38" s="16"/>
     </row>
     <row r="39" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="16"/>
-      <c r="C39" s="16"/>
-      <c r="D39" s="16"/>
-      <c r="E39" s="16"/>
-      <c r="F39" s="16"/>
-      <c r="G39" s="17"/>
-      <c r="H39" s="17"/>
-      <c r="I39" s="17"/>
-      <c r="J39" s="17"/>
-      <c r="K39" s="17"/>
-      <c r="L39" s="17"/>
+      <c r="B39" s="15"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="15"/>
+      <c r="G39" s="16"/>
+      <c r="H39" s="16"/>
+      <c r="I39" s="16"/>
+      <c r="J39" s="16"/>
+      <c r="K39" s="16"/>
+      <c r="L39" s="16"/>
     </row>
     <row r="40" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="16"/>
-      <c r="C40" s="16"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16"/>
-      <c r="G40" s="17"/>
-      <c r="H40" s="17"/>
-      <c r="I40" s="17"/>
-      <c r="J40" s="17"/>
-      <c r="K40" s="17"/>
-      <c r="L40" s="17"/>
+      <c r="B40" s="15"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="16"/>
+      <c r="H40" s="16"/>
+      <c r="I40" s="16"/>
+      <c r="J40" s="16"/>
+      <c r="K40" s="16"/>
+      <c r="L40" s="16"/>
     </row>
     <row r="41" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="16"/>
-      <c r="C41" s="16"/>
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="16"/>
-      <c r="G41" s="17"/>
-      <c r="H41" s="17"/>
-      <c r="I41" s="17"/>
-      <c r="J41" s="17"/>
-      <c r="K41" s="17"/>
-      <c r="L41" s="17"/>
+      <c r="B41" s="15"/>
+      <c r="C41" s="15"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="16"/>
+      <c r="H41" s="16"/>
+      <c r="I41" s="16"/>
+      <c r="J41" s="16"/>
+      <c r="K41" s="16"/>
+      <c r="L41" s="16"/>
     </row>
     <row r="42" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="16"/>
-      <c r="C42" s="16"/>
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="17"/>
-      <c r="H42" s="17"/>
-      <c r="I42" s="17"/>
-      <c r="J42" s="17"/>
-      <c r="K42" s="17"/>
-      <c r="L42" s="17"/>
+      <c r="B42" s="15"/>
+      <c r="C42" s="15"/>
+      <c r="D42" s="15"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="16"/>
+      <c r="H42" s="16"/>
+      <c r="I42" s="16"/>
+      <c r="J42" s="16"/>
+      <c r="K42" s="16"/>
+      <c r="L42" s="16"/>
     </row>
     <row r="43" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="16"/>
-      <c r="C43" s="16"/>
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
-      <c r="F43" s="16"/>
-      <c r="G43" s="17"/>
-      <c r="H43" s="17"/>
-      <c r="I43" s="17"/>
-      <c r="J43" s="17"/>
-      <c r="K43" s="17"/>
-      <c r="L43" s="17"/>
+      <c r="B43" s="15"/>
+      <c r="C43" s="15"/>
+      <c r="D43" s="15"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="15"/>
+      <c r="G43" s="16"/>
+      <c r="H43" s="16"/>
+      <c r="I43" s="16"/>
+      <c r="J43" s="16"/>
+      <c r="K43" s="16"/>
+      <c r="L43" s="16"/>
     </row>
     <row r="44" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="16"/>
-      <c r="C44" s="16"/>
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="16"/>
-      <c r="G44" s="17"/>
-      <c r="H44" s="17"/>
-      <c r="I44" s="17"/>
-      <c r="J44" s="17"/>
-      <c r="K44" s="17"/>
-      <c r="L44" s="17"/>
+      <c r="B44" s="15"/>
+      <c r="C44" s="15"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="15"/>
+      <c r="G44" s="16"/>
+      <c r="H44" s="16"/>
+      <c r="I44" s="16"/>
+      <c r="J44" s="16"/>
+      <c r="K44" s="16"/>
+      <c r="L44" s="16"/>
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="18" t="s">
+      <c r="B45" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="C45" s="19" t="n">
+      <c r="C45" s="18" t="n">
         <f aca="false">SUM(C8:C44)</f>
         <v>0</v>
       </c>
-      <c r="D45" s="20"/>
-      <c r="E45" s="20"/>
-      <c r="F45" s="20"/>
-      <c r="G45" s="20"/>
-      <c r="H45" s="20"/>
-      <c r="I45" s="20"/>
-      <c r="J45" s="20"/>
-      <c r="K45" s="20"/>
-      <c r="L45" s="20"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="B47" s="21"/>
-      <c r="C47" s="21"/>
-      <c r="D47" s="21"/>
-      <c r="E47" s="21"/>
-      <c r="F47" s="21"/>
-      <c r="G47" s="21"/>
-      <c r="H47" s="21"/>
-      <c r="I47" s="21"/>
-      <c r="J47" s="21"/>
-      <c r="K47" s="21"/>
-      <c r="L47" s="21"/>
+      <c r="D45" s="19"/>
+      <c r="E45" s="19"/>
+      <c r="F45" s="19"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="19"/>
+      <c r="I45" s="19"/>
+      <c r="J45" s="19"/>
+      <c r="K45" s="19"/>
+      <c r="L45" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="B2:L2"/>
     <mergeCell ref="B7:L7"/>
     <mergeCell ref="B14:L14"/>
-    <mergeCell ref="A47:L47"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1703,397 +1667,397 @@
   <dimension ref="B1:D62"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="3"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
+      <c r="B2" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
     </row>
     <row r="3" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+    </row>
+    <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-    </row>
-    <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="24" t="s">
+      <c r="C5" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="D5" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="24" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="15"/>
+      <c r="D6" s="16"/>
+    </row>
+    <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="17"/>
-    </row>
-    <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="25" t="s">
+      <c r="C7" s="15"/>
+      <c r="D7" s="16"/>
+    </row>
+    <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C7" s="16"/>
-      <c r="D7" s="17"/>
-    </row>
-    <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="15"/>
+      <c r="D8" s="16"/>
+    </row>
+    <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="17"/>
-    </row>
-    <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="25" t="s">
+      <c r="C9" s="15"/>
+      <c r="D9" s="16"/>
+    </row>
+    <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C9" s="16"/>
-      <c r="D9" s="17"/>
-    </row>
-    <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="15"/>
+      <c r="D10" s="16"/>
+    </row>
+    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17"/>
-    </row>
-    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="25" t="s">
+      <c r="C11" s="15"/>
+      <c r="D11" s="16"/>
+    </row>
+    <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="17"/>
-    </row>
-    <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" s="16"/>
-      <c r="D12" s="17"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="16"/>
     </row>
     <row r="13" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="26" t="s">
+      <c r="B14" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+    </row>
+    <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-    </row>
-    <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="D15" s="24" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="15"/>
+      <c r="D16" s="16"/>
+    </row>
+    <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="17"/>
-    </row>
-    <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="25" t="s">
+      <c r="C17" s="15"/>
+      <c r="D17" s="16"/>
+    </row>
+    <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="17"/>
-    </row>
-    <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="15"/>
+      <c r="D18" s="16"/>
+    </row>
+    <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="17"/>
-    </row>
-    <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="25" t="s">
+      <c r="C19" s="15"/>
+      <c r="D19" s="16"/>
+    </row>
+    <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C19" s="16"/>
-      <c r="D19" s="17"/>
-    </row>
-    <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20" s="16"/>
-      <c r="D20" s="17"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="16"/>
     </row>
     <row r="21" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="27" t="s">
+      <c r="B22" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+    </row>
+    <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C22" s="27"/>
-      <c r="D22" s="27"/>
-    </row>
-    <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="C23" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="D23" s="24" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" s="16"/>
-      <c r="D24" s="17"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="16"/>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="25"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="17"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="16"/>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="3"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="16"/>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="25"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="17"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="16"/>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="3"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="17"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="16"/>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="25"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="17"/>
+      <c r="B29" s="23"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="16"/>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="3"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="17"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="16"/>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="25"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="17"/>
+      <c r="B31" s="23"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="16"/>
     </row>
     <row r="32" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="28" t="s">
+      <c r="B33" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="C33" s="26"/>
+      <c r="D33" s="26"/>
+    </row>
+    <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C34" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="D34" s="22" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-    </row>
-    <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="C34" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="D34" s="24" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="25" t="s">
+      <c r="C35" s="15"/>
+      <c r="D35" s="16"/>
+    </row>
+    <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B36" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C35" s="16"/>
-      <c r="D35" s="17"/>
-    </row>
-    <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="15"/>
+      <c r="D36" s="16"/>
+    </row>
+    <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B37" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="C36" s="16"/>
-      <c r="D36" s="17"/>
-    </row>
-    <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="25" t="s">
+      <c r="C37" s="15"/>
+      <c r="D37" s="16"/>
+    </row>
+    <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C37" s="16"/>
-      <c r="D37" s="17"/>
-    </row>
-    <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C38" s="16"/>
-      <c r="D38" s="17"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="16"/>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="25"/>
-      <c r="C39" s="16"/>
-      <c r="D39" s="17"/>
+      <c r="B39" s="23"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="16"/>
     </row>
     <row r="40" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="29" t="s">
+      <c r="B41" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="C41" s="27"/>
+      <c r="D41" s="27"/>
+    </row>
+    <row r="42" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B42" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C42" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="D42" s="22" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B43" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="C41" s="29"/>
-      <c r="D41" s="29"/>
-    </row>
-    <row r="42" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="C42" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="D42" s="24" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="25" t="s">
+      <c r="C43" s="15"/>
+      <c r="D43" s="16"/>
+    </row>
+    <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B44" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C43" s="16"/>
-      <c r="D43" s="17"/>
-    </row>
-    <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="3" t="s">
+      <c r="C44" s="15"/>
+      <c r="D44" s="16"/>
+    </row>
+    <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B45" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="C44" s="16"/>
-      <c r="D44" s="17"/>
-    </row>
-    <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="25" t="s">
+      <c r="C45" s="15"/>
+      <c r="D45" s="16"/>
+    </row>
+    <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B46" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C45" s="16"/>
-      <c r="D45" s="17"/>
-    </row>
-    <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="3" t="s">
+      <c r="C46" s="15"/>
+      <c r="D46" s="16"/>
+    </row>
+    <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B47" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="C46" s="16"/>
-      <c r="D46" s="17"/>
-    </row>
-    <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="C47" s="16"/>
-      <c r="D47" s="17"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="16"/>
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="3"/>
-      <c r="C48" s="16"/>
-      <c r="D48" s="17"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="15"/>
+      <c r="D48" s="16"/>
     </row>
     <row r="49" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="30" t="s">
+      <c r="B50" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="C50" s="28"/>
+      <c r="D50" s="28"/>
+    </row>
+    <row r="51" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B51" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C51" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="D51" s="22" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B52" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C50" s="30"/>
-      <c r="D50" s="30"/>
-    </row>
-    <row r="51" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B51" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="C51" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="D51" s="24" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="3" t="s">
+      <c r="C52" s="15"/>
+      <c r="D52" s="16"/>
+    </row>
+    <row r="53" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B53" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="C52" s="16"/>
-      <c r="D52" s="17"/>
-    </row>
-    <row r="53" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="C53" s="16"/>
-      <c r="D53" s="17"/>
+      <c r="C53" s="15"/>
+      <c r="D53" s="16"/>
     </row>
     <row r="54" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B54" s="3"/>
-      <c r="C54" s="16"/>
-      <c r="D54" s="17"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="15"/>
+      <c r="D54" s="16"/>
     </row>
     <row r="55" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B56" s="30" t="s">
+      <c r="B56" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="C56" s="28"/>
+      <c r="D56" s="28"/>
+    </row>
+    <row r="57" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B57" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C57" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="D57" s="22" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B58" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C56" s="30"/>
-      <c r="D56" s="30"/>
-    </row>
-    <row r="57" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B57" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="C57" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="D57" s="24" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B58" s="3" t="s">
+      <c r="C58" s="15"/>
+      <c r="D58" s="16"/>
+    </row>
+    <row r="59" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B59" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="C58" s="16"/>
-      <c r="D58" s="17"/>
-    </row>
-    <row r="59" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B59" s="25" t="s">
+      <c r="C59" s="15"/>
+      <c r="D59" s="16"/>
+    </row>
+    <row r="60" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B60" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C59" s="16"/>
-      <c r="D59" s="17"/>
-    </row>
-    <row r="60" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B60" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C60" s="16"/>
-      <c r="D60" s="17"/>
+      <c r="C60" s="15"/>
+      <c r="D60" s="16"/>
     </row>
     <row r="61" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B61" s="25"/>
-      <c r="C61" s="16"/>
-      <c r="D61" s="17"/>
+      <c r="B61" s="23"/>
+      <c r="C61" s="15"/>
+      <c r="D61" s="16"/>
     </row>
     <row r="62" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
